--- a/backend/projects.xlsx
+++ b/backend/projects.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -499,9 +499,259 @@
         <v>2025-04-14T07:41:02.444Z</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Starwire Industries</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Certification of Nickel Alloys</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2023-2024</v>
+      </c>
+      <c r="E3">
+        <v>800000</v>
+      </c>
+      <c r="F3">
+        <v>500000</v>
+      </c>
+      <c r="G3" t="str">
+        <v>jay shree ram</v>
+      </c>
+      <c r="H3" t="str">
+        <v xml:space="preserve">om mani padme hum </v>
+      </c>
+      <c r="I3" t="str">
+        <v>Dr John Doe</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Dr Jane Doe</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Dr Rajesh Ganesh</v>
+      </c>
+      <c r="L3" t="str">
+        <v>rajganesh@gmail.com</v>
+      </c>
+      <c r="M3" t="str">
+        <v>1744624304766-bill.pdf</v>
+      </c>
+      <c r="N3" t="str">
+        <v>1744624304767-bill.pdf</v>
+      </c>
+      <c r="O3" t="str">
+        <v>bhuvana@ssn.edu.in</v>
+      </c>
+      <c r="P3" t="str">
+        <v>2025-04-14T09:51:44.774Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ABC Solutions</v>
+      </c>
+      <c r="C4" t="str">
+        <v>AI model solution</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2023-2024</v>
+      </c>
+      <c r="E4">
+        <v>80000</v>
+      </c>
+      <c r="F4">
+        <v>70000</v>
+      </c>
+      <c r="G4" t="str">
+        <v>jay shree ram</v>
+      </c>
+      <c r="H4" t="str">
+        <v>hare ram</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Dr John Doe</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Dr Jane Doe</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Dr Raj</v>
+      </c>
+      <c r="L4" t="str">
+        <v>raj@gmail.com</v>
+      </c>
+      <c r="M4" t="str">
+        <v>1744624399077-bill.pdf</v>
+      </c>
+      <c r="N4" t="str">
+        <v>1744624399077-bill.pdf</v>
+      </c>
+      <c r="O4" t="str">
+        <v>bhuvana@ssn.edu.in</v>
+      </c>
+      <c r="P4" t="str">
+        <v>2025-04-14T09:53:19.081Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v xml:space="preserve">XYZ </v>
+      </c>
+      <c r="C5" t="str">
+        <v>Oil Refinery</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2024-2025</v>
+      </c>
+      <c r="E5">
+        <v>40000</v>
+      </c>
+      <c r="F5">
+        <v>30000</v>
+      </c>
+      <c r="G5" t="str">
+        <v>jay shree ram</v>
+      </c>
+      <c r="H5" t="str">
+        <v>om mani pay mey hun</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Dr John Doe</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Dr Jane Doe</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Dr Murugan</v>
+      </c>
+      <c r="L5" t="str">
+        <v>murugan@gmail.com</v>
+      </c>
+      <c r="M5" t="str">
+        <v>1744624662609-bill.pdf</v>
+      </c>
+      <c r="N5" t="str">
+        <v>1744624662609-bill.pdf</v>
+      </c>
+      <c r="O5" t="str">
+        <v>someone@ssn.edu.in</v>
+      </c>
+      <c r="P5" t="str">
+        <v>2025-04-14T09:57:42.612Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v xml:space="preserve">XYZ </v>
+      </c>
+      <c r="C6" t="str">
+        <v>Oil Refinery</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2024-2025</v>
+      </c>
+      <c r="E6">
+        <v>80000</v>
+      </c>
+      <c r="F6">
+        <v>75000</v>
+      </c>
+      <c r="G6" t="str">
+        <v>jay ram</v>
+      </c>
+      <c r="H6" t="str">
+        <v>om sai ram</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Dr Krishnan</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Dr Radha</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Dr Murugan</v>
+      </c>
+      <c r="L6" t="str">
+        <v>murugan@gmail.com</v>
+      </c>
+      <c r="M6" t="str">
+        <v>1744624709394-bill.pdf</v>
+      </c>
+      <c r="N6" t="str">
+        <v>1744624709394-bill.pdf</v>
+      </c>
+      <c r="O6" t="str">
+        <v>someone@ssn.edu.in</v>
+      </c>
+      <c r="P6" t="str">
+        <v>2025-04-14T09:58:29.398Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v xml:space="preserve">ABC Solutions </v>
+      </c>
+      <c r="C7" t="str">
+        <v>AI model solution</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2024-2025</v>
+      </c>
+      <c r="E7">
+        <v>80000</v>
+      </c>
+      <c r="F7">
+        <v>75000</v>
+      </c>
+      <c r="G7" t="str">
+        <v>om sri</v>
+      </c>
+      <c r="H7" t="str">
+        <v>ram</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Dr Krishnan</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Dr Radha</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Dr Murugan</v>
+      </c>
+      <c r="L7" t="str">
+        <v>murugan@gmail.com</v>
+      </c>
+      <c r="M7" t="str">
+        <v>1744624743610-bill.pdf</v>
+      </c>
+      <c r="N7" t="str">
+        <v>1744624743611-bill.pdf</v>
+      </c>
+      <c r="O7" t="str">
+        <v>someone@ssn.edu.in</v>
+      </c>
+      <c r="P7" t="str">
+        <v>2025-04-14T09:59:03.614Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/projects.xlsx
+++ b/backend/projects.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -749,9 +749,59 @@
         <v>2025-04-14T09:59:03.614Z</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v xml:space="preserve">Ganesha industries </v>
+      </c>
+      <c r="C8" t="str">
+        <v>Oil Refinery</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2024-2025</v>
+      </c>
+      <c r="E8">
+        <v>80000</v>
+      </c>
+      <c r="F8">
+        <v>75000</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Ram Sham Sita</v>
+      </c>
+      <c r="H8" t="str">
+        <v>this is project based on certification of oil refinery</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Dr Krishnan</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Dr Radha</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Dr Murugan</v>
+      </c>
+      <c r="L8" t="str">
+        <v>murugan@gmail.com</v>
+      </c>
+      <c r="M8" t="str">
+        <v>1744629327054-bill.pdf</v>
+      </c>
+      <c r="N8" t="str">
+        <v>1744629327054-bill.pdf</v>
+      </c>
+      <c r="O8" t="str">
+        <v>bhuvana@ssn.edu.in</v>
+      </c>
+      <c r="P8" t="str">
+        <v>2025-04-14T11:15:27.061Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/projects.xlsx
+++ b/backend/projects.xlsx
@@ -1,41 +1,272 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\college\SSN\SEM 6\ip\minipro\ip-mini\backend\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A373F881-2F9A-4210-9F2B-F89908E1202B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>industryName</t>
+  </si>
+  <si>
+    <t>projectTitle</t>
+  </si>
+  <si>
+    <t>academicYear</t>
+  </si>
+  <si>
+    <t>amountSanctioned</t>
+  </si>
+  <si>
+    <t>amountReceived</t>
+  </si>
+  <si>
+    <t>studentDetails</t>
+  </si>
+  <si>
+    <t>projectSummary</t>
+  </si>
+  <si>
+    <t>principalInvestigator</t>
+  </si>
+  <si>
+    <t>coPrincipalInvestigator</t>
+  </si>
+  <si>
+    <t>facultyName</t>
+  </si>
+  <si>
+    <t>facultyId</t>
+  </si>
+  <si>
+    <t>billSettlementFile</t>
+  </si>
+  <si>
+    <t>agreementFile</t>
+  </si>
+  <si>
+    <t>createdBy</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
+  <si>
+    <t>ABC Solutions</t>
+  </si>
+  <si>
+    <t>AI Model Solution</t>
+  </si>
+  <si>
+    <t>2023-2024</t>
+  </si>
+  <si>
+    <t>jay shree ram</t>
+  </si>
+  <si>
+    <t>har har mahadev</t>
+  </si>
+  <si>
+    <t>Dr Krishnan</t>
+  </si>
+  <si>
+    <t>Dr Radha</t>
+  </si>
+  <si>
+    <t>Dr Raj Ganesh</t>
+  </si>
+  <si>
+    <t>rajganesh@gmail.com</t>
+  </si>
+  <si>
+    <t>1744616462430-bill.pdf</t>
+  </si>
+  <si>
+    <t>1744616462434-bill.pdf</t>
+  </si>
+  <si>
+    <t>bhuvana@ssn.edu.in</t>
+  </si>
+  <si>
+    <t>2025-04-14T07:41:02.444Z</t>
+  </si>
+  <si>
+    <t>Starwire Industries</t>
+  </si>
+  <si>
+    <t>Certification of Nickel Alloys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">om mani padme hum </t>
+  </si>
+  <si>
+    <t>Dr John Doe</t>
+  </si>
+  <si>
+    <t>Dr Jane Doe</t>
+  </si>
+  <si>
+    <t>Dr Rajesh Ganesh</t>
+  </si>
+  <si>
+    <t>1744624304766-bill.pdf</t>
+  </si>
+  <si>
+    <t>1744624304767-bill.pdf</t>
+  </si>
+  <si>
+    <t>2025-04-14T09:51:44.774Z</t>
+  </si>
+  <si>
+    <t>AI model solution</t>
+  </si>
+  <si>
+    <t>hare ram</t>
+  </si>
+  <si>
+    <t>Dr Raj</t>
+  </si>
+  <si>
+    <t>raj@gmail.com</t>
+  </si>
+  <si>
+    <t>1744624399077-bill.pdf</t>
+  </si>
+  <si>
+    <t>2025-04-14T09:53:19.081Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XYZ </t>
+  </si>
+  <si>
+    <t>Oil Refinery</t>
+  </si>
+  <si>
+    <t>2024-2025</t>
+  </si>
+  <si>
+    <t>om mani pay mey hun</t>
+  </si>
+  <si>
+    <t>Dr Murugan</t>
+  </si>
+  <si>
+    <t>murugan@gmail.com</t>
+  </si>
+  <si>
+    <t>1744624662609-bill.pdf</t>
+  </si>
+  <si>
+    <t>someone@ssn.edu.in</t>
+  </si>
+  <si>
+    <t>2025-04-14T09:57:42.612Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABC Solutions </t>
+  </si>
+  <si>
+    <t>om sri</t>
+  </si>
+  <si>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>1744624743610-bill.pdf</t>
+  </si>
+  <si>
+    <t>1744624743611-bill.pdf</t>
+  </si>
+  <si>
+    <t>2025-04-14T09:59:03.614Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganesha industries </t>
+  </si>
+  <si>
+    <t>Ram Sham Sita</t>
+  </si>
+  <si>
+    <t>this is project based on certification of oil refinery</t>
+  </si>
+  <si>
+    <t>1744629327054-bill.pdf</t>
+  </si>
+  <si>
+    <t>2025-04-14T11:15:27.061Z</t>
+  </si>
+  <si>
+    <t>Certification of ATF</t>
+  </si>
+  <si>
+    <t>hari om</t>
+  </si>
+  <si>
+    <t>1744636701252-bill.pdf</t>
+  </si>
+  <si>
+    <t>shreya@ssn.edu.in</t>
+  </si>
+  <si>
+    <t>2025-04-14T13:18:21.256Z</t>
+  </si>
+  <si>
+    <t>PQR Pvt Ltd</t>
+  </si>
+  <si>
+    <t>jker guioryurfuhj</t>
+  </si>
+  <si>
+    <t>er ghbrfgbtc  gty</t>
+  </si>
+  <si>
+    <t>Dr Watson</t>
+  </si>
+  <si>
+    <t>Dr Lara</t>
+  </si>
+  <si>
+    <t>Dr Mary</t>
+  </si>
+  <si>
+    <t>mary@gmail.com</t>
+  </si>
+  <si>
+    <t>1744639551155-bill.pdf</t>
+  </si>
+  <si>
+    <t>1744639551156-bill.pdf</t>
+  </si>
+  <si>
+    <t>nikisai.003@gmail.com</t>
+  </si>
+  <si>
+    <t>2025-04-14T14:05:51.161Z</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +296,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,71 +635,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>industryName</v>
-      </c>
-      <c r="C1" t="str">
-        <v>projectTitle</v>
-      </c>
-      <c r="D1" t="str">
-        <v>academicYear</v>
-      </c>
-      <c r="E1" t="str">
-        <v>amountSanctioned</v>
-      </c>
-      <c r="F1" t="str">
-        <v>amountReceived</v>
-      </c>
-      <c r="G1" t="str">
-        <v>studentDetails</v>
-      </c>
-      <c r="H1" t="str">
-        <v>projectSummary</v>
-      </c>
-      <c r="I1" t="str">
-        <v>principalInvestigator</v>
-      </c>
-      <c r="J1" t="str">
-        <v>coPrincipalInvestigator</v>
-      </c>
-      <c r="K1" t="str">
-        <v>facultyName</v>
-      </c>
-      <c r="L1" t="str">
-        <v>facultyId</v>
-      </c>
-      <c r="M1" t="str">
-        <v>billSettlementFile</v>
-      </c>
-      <c r="N1" t="str">
-        <v>agreementFile</v>
-      </c>
-      <c r="O1" t="str">
-        <v>createdBy</v>
-      </c>
-      <c r="P1" t="str">
-        <v>createdAt</v>
+    <row r="1" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>ABC Solutions</v>
-      </c>
-      <c r="C2" t="str">
-        <v>AI Model Solution</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2023-2024</v>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
       </c>
       <c r="E2">
         <v>100000</v>
@@ -468,49 +708,49 @@
       <c r="F2">
         <v>90000</v>
       </c>
-      <c r="G2" t="str">
-        <v>jay shree ram</v>
-      </c>
-      <c r="H2" t="str">
-        <v>har har mahadev</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Dr Krishnan</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Dr Radha</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Dr Raj</v>
-      </c>
-      <c r="L2" t="str">
-        <v>raj@gmail.com</v>
-      </c>
-      <c r="M2" t="str">
-        <v>1744616462430-bill.pdf</v>
-      </c>
-      <c r="N2" t="str">
-        <v>1744616462434-bill.pdf</v>
-      </c>
-      <c r="O2" t="str">
-        <v>bhuvana@ssn.edu.in</v>
-      </c>
-      <c r="P2" t="str">
-        <v>2025-04-14T07:41:02.444Z</v>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Starwire Industries</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Certification of Nickel Alloys</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2023-2024</v>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
       </c>
       <c r="E3">
         <v>800000</v>
@@ -518,49 +758,49 @@
       <c r="F3">
         <v>500000</v>
       </c>
-      <c r="G3" t="str">
-        <v>jay shree ram</v>
-      </c>
-      <c r="H3" t="str">
-        <v xml:space="preserve">om mani padme hum </v>
-      </c>
-      <c r="I3" t="str">
-        <v>Dr John Doe</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Dr Jane Doe</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Dr Rajesh Ganesh</v>
-      </c>
-      <c r="L3" t="str">
-        <v>rajganesh@gmail.com</v>
-      </c>
-      <c r="M3" t="str">
-        <v>1744624304766-bill.pdf</v>
-      </c>
-      <c r="N3" t="str">
-        <v>1744624304767-bill.pdf</v>
-      </c>
-      <c r="O3" t="str">
-        <v>bhuvana@ssn.edu.in</v>
-      </c>
-      <c r="P3" t="str">
-        <v>2025-04-14T09:51:44.774Z</v>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>ABC Solutions</v>
-      </c>
-      <c r="C4" t="str">
-        <v>AI model solution</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2023-2024</v>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
       </c>
       <c r="E4">
         <v>80000</v>
@@ -568,99 +808,99 @@
       <c r="F4">
         <v>70000</v>
       </c>
-      <c r="G4" t="str">
-        <v>jay shree ram</v>
-      </c>
-      <c r="H4" t="str">
-        <v>hare ram</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Dr John Doe</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Dr Jane Doe</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Dr Raj</v>
-      </c>
-      <c r="L4" t="str">
-        <v>raj@gmail.com</v>
-      </c>
-      <c r="M4" t="str">
-        <v>1744624399077-bill.pdf</v>
-      </c>
-      <c r="N4" t="str">
-        <v>1744624399077-bill.pdf</v>
-      </c>
-      <c r="O4" t="str">
-        <v>bhuvana@ssn.edu.in</v>
-      </c>
-      <c r="P4" t="str">
-        <v>2025-04-14T09:53:19.081Z</v>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v xml:space="preserve">XYZ </v>
-      </c>
-      <c r="C5" t="str">
-        <v>Oil Refinery</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2024-2025</v>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F5">
-        <v>30000</v>
-      </c>
-      <c r="G5" t="str">
-        <v>jay shree ram</v>
-      </c>
-      <c r="H5" t="str">
-        <v>om mani pay mey hun</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Dr John Doe</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Dr Jane Doe</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Dr Murugan</v>
-      </c>
-      <c r="L5" t="str">
-        <v>murugan@gmail.com</v>
-      </c>
-      <c r="M5" t="str">
-        <v>1744624662609-bill.pdf</v>
-      </c>
-      <c r="N5" t="str">
-        <v>1744624662609-bill.pdf</v>
-      </c>
-      <c r="O5" t="str">
-        <v>someone@ssn.edu.in</v>
-      </c>
-      <c r="P5" t="str">
-        <v>2025-04-14T09:57:42.612Z</v>
+        <v>70000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v xml:space="preserve">XYZ </v>
-      </c>
-      <c r="C6" t="str">
-        <v>Oil Refinery</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2024-2025</v>
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
       </c>
       <c r="E6">
         <v>80000</v>
@@ -668,49 +908,49 @@
       <c r="F6">
         <v>75000</v>
       </c>
-      <c r="G6" t="str">
-        <v>jay ram</v>
-      </c>
-      <c r="H6" t="str">
-        <v>om sai ram</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Dr Krishnan</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Dr Radha</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Dr Murugan</v>
-      </c>
-      <c r="L6" t="str">
-        <v>murugan@gmail.com</v>
-      </c>
-      <c r="M6" t="str">
-        <v>1744624709394-bill.pdf</v>
-      </c>
-      <c r="N6" t="str">
-        <v>1744624709394-bill.pdf</v>
-      </c>
-      <c r="O6" t="str">
-        <v>someone@ssn.edu.in</v>
-      </c>
-      <c r="P6" t="str">
-        <v>2025-04-14T09:58:29.398Z</v>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v xml:space="preserve">ABC Solutions </v>
-      </c>
-      <c r="C7" t="str">
-        <v>AI model solution</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2024-2025</v>
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
       </c>
       <c r="E7">
         <v>80000</v>
@@ -718,49 +958,49 @@
       <c r="F7">
         <v>75000</v>
       </c>
-      <c r="G7" t="str">
-        <v>om sri</v>
-      </c>
-      <c r="H7" t="str">
-        <v>ram</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Dr Krishnan</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Dr Radha</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Dr Murugan</v>
-      </c>
-      <c r="L7" t="str">
-        <v>murugan@gmail.com</v>
-      </c>
-      <c r="M7" t="str">
-        <v>1744624743610-bill.pdf</v>
-      </c>
-      <c r="N7" t="str">
-        <v>1744624743611-bill.pdf</v>
-      </c>
-      <c r="O7" t="str">
-        <v>someone@ssn.edu.in</v>
-      </c>
-      <c r="P7" t="str">
-        <v>2025-04-14T09:59:03.614Z</v>
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
-        <v xml:space="preserve">Ganesha industries </v>
-      </c>
-      <c r="C8" t="str">
-        <v>Oil Refinery</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2024-2025</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
       </c>
       <c r="E8">
         <v>80000</v>
@@ -768,40 +1008,91 @@
       <c r="F8">
         <v>75000</v>
       </c>
-      <c r="G8" t="str">
-        <v>Ram Sham Sita</v>
-      </c>
-      <c r="H8" t="str">
-        <v>this is project based on certification of oil refinery</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Dr Krishnan</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Dr Radha</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Dr Murugan</v>
-      </c>
-      <c r="L8" t="str">
-        <v>murugan@gmail.com</v>
-      </c>
-      <c r="M8" t="str">
-        <v>1744629327054-bill.pdf</v>
-      </c>
-      <c r="N8" t="str">
-        <v>1744629327054-bill.pdf</v>
-      </c>
-      <c r="O8" t="str">
-        <v>bhuvana@ssn.edu.in</v>
-      </c>
-      <c r="P8" t="str">
-        <v>2025-04-14T11:15:27.061Z</v>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" t="s">
+        <v>67</v>
+      </c>
+      <c r="P8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>80000</v>
+      </c>
+      <c r="F9">
+        <v>75000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M9" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P9" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P8"/>
+    <ignoredError sqref="A1:P9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>